--- a/ket_qua.xlsx
+++ b/ket_qua.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,6 +489,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>M0261613371,NGUYEN THI MY DUYEN,NGUYEN THI MY DUYEN chuyen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>098ITC1261260004</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NGUYEN THI MY DUYEN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>114355615</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>NGUYEN THI MY DUYEN 1613371</t>
         </is>
       </c>
     </row>

--- a/ket_qua.xlsx
+++ b/ket_qua.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,11 @@
           <t>Nội dung thanh toán</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,11 +476,7 @@
           <t>213116324342575.010001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>NGUYEN THI MY DUYEN</t>
@@ -489,6 +490,11 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>M0261613371,NGUYEN THI MY DUYEN,NGUYEN THI MY DUYEN chuyen</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Techcombank</t>
         </is>
       </c>
     </row>
@@ -517,6 +523,11 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>NGUYEN THI MY DUYEN 1613371</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TPBank</t>
         </is>
       </c>
     </row>
